--- a/esyluban/examples/dev/DataTables/test/demo_group.xlsx
+++ b/esyluban/examples/dev/DataTables/test/demo_group.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbDemoGroup" &amp; value_type="test.DemoGroup" &amp; read_schema_from_file="false" &amp; input="TbDemoGroup@test/demo_group.xlsx" &amp; output="test_tbdemogroup"</t>
+          <t>full_name="test.TbDemoGroup"</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbDemoGroup_C" &amp; value_type="test.DemoGroup" &amp; read_schema_from_file="false" &amp; input="TbDemoGroup_C@test/demo_group.xlsx" &amp; output="test_tbdemogroup_c" &amp; group="c"</t>
+          <t>full_name="test.TbDemoGroup_C" &amp; value_type="test.DemoGroup" &amp; group="c"</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbDemoGroup_S" &amp; value_type="test.DemoGroup" &amp; read_schema_from_file="false" &amp; input="TbDemoGroup_S@test/demo_group.xlsx" &amp; output="test_tbdemogroup_s" &amp; group="s"</t>
+          <t>full_name="test.TbDemoGroup_S" &amp; value_type="test.DemoGroup" &amp; group="s"</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbDemoGroup_E" &amp; value_type="test.DemoGroup" &amp; read_schema_from_file="false" &amp; input="TbDemoGroup_E@test/demo_group.xlsx" &amp; output="test_tbdemogroup_e" &amp; group="e"</t>
+          <t>full_name="test.TbDemoGroup_E" &amp; value_type="test.DemoGroup" &amp; group="e"</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbDemoGroup_T" &amp; value_type="test.DemoGroup" &amp; read_schema_from_file="false" &amp; input="TbDemoGroup_T@test/demo_group.xlsx" &amp; output="test_tbdemogroup_t" &amp; group="t"</t>
+          <t>full_name="test.TbDemoGroup_T" &amp; value_type="test.DemoGroup" &amp; group="t"</t>
         </is>
       </c>
     </row>

--- a/esyluban/examples/dev/DataTables/test/demo_group.xlsx
+++ b/esyluban/examples/dev/DataTables/test/demo_group.xlsx
@@ -637,7 +637,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -827,7 +827,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1017,7 +1017,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1207,7 +1207,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1397,7 +1397,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
